--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039486</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039487</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763374</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763375</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322962</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1823,6 +1873,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322963</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763368</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2183,6 +2248,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322965</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2303,6 +2373,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1323582</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2419,6 +2494,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1568573</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2539,6 +2619,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763371</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,8 +2734,32 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039486</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039492</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039487</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039486</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039492</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039487</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1763367</v>
+        <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,46 +1517,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Malarna, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647086</v>
+        <v>647044</v>
       </c>
       <c r="R9" t="n">
-        <v>6943195</v>
+        <v>6943285</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,12 +1571,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,45 +1597,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763367</t>
+          <t>https://artportalen.se/Sighting/136492696</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1322962</v>
+        <v>1763367</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,26 +1629,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1671,14 +1658,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Malarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647245</v>
+        <v>647086</v>
       </c>
       <c r="R10" t="n">
-        <v>6943405</v>
+        <v>6943195</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,16 +1737,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322962</t>
+          <t>https://artportalen.se/Sighting/1763367</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1322963</v>
+        <v>136492698</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,46 +1754,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647228</v>
+        <v>647146</v>
       </c>
       <c r="R11" t="n">
-        <v>6943441</v>
+        <v>6942982</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,12 +1816,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall. På bilden syns det äldre ringhacket, men det färska som sitter strax ovanför syns desto sämre. Med kikare i fält syns det färska ringhacket betydligt bättre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,45 +1847,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/136492698</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1763368</v>
+        <v>136492701</v>
       </c>
       <c r="B12" t="n">
-        <v>93235</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,46 +1879,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647245</v>
+        <v>647146</v>
       </c>
       <c r="R12" t="n">
-        <v>6943405</v>
+        <v>6942952</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,12 +1938,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,45 +1969,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763368</t>
+          <t>https://artportalen.se/Sighting/136492701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1763369</v>
+        <v>136492702</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,46 +2001,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647228</v>
+        <v>647143</v>
       </c>
       <c r="R13" t="n">
-        <v>6943441</v>
+        <v>6942924</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2080,12 +2060,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,45 +2091,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/136492702</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1322965</v>
+        <v>136492704</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,46 +2123,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647065</v>
+        <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6943550</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2205,12 +2185,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 2 meter ovan mark i asp. Hade inget måttband med mig varför bohålsdiametern inte kunde mätas. Hålet såg dock relativt litet ut varför jag bedömer det som sannolikt uthackat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,92 +2216,78 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322965</t>
+          <t>https://artportalen.se/Sighting/136492704</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1323582</v>
+        <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>99341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lomtjärn S, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646475</v>
+        <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942960</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,12 +2311,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,45 +2337,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323582</t>
+          <t>https://artportalen.se/Sighting/136492703</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1568573</v>
+        <v>1322962</v>
       </c>
       <c r="B16" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,34 +2369,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lomtjärnen S - Malarna, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646461</v>
+        <v>647245</v>
       </c>
       <c r="R16" t="n">
-        <v>6942878</v>
+        <v>6943405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,12 +2432,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,12 +2456,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>hällmarkstallskog, nyckelbiotopsklass</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2496,16 +2477,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1568573</t>
+          <t>https://artportalen.se/Sighting/1322962</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1763371</v>
+        <v>1322963</v>
       </c>
       <c r="B17" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,26 +2494,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2546,10 +2527,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647088</v>
+        <v>647228</v>
       </c>
       <c r="R17" t="n">
-        <v>6943543</v>
+        <v>6943441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2621,13 +2602,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763371</t>
+          <t>https://artportalen.se/Sighting/1322963</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1763372</v>
+        <v>1763368</v>
       </c>
       <c r="B18" t="n">
         <v>93235</v>
@@ -2657,7 +2638,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2671,10 +2652,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647055</v>
+        <v>647245</v>
       </c>
       <c r="R18" t="n">
-        <v>6943589</v>
+        <v>6943405</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,6 +2699,16 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -2736,7 +2727,1206 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/1763368</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1763369</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>647228</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6943441</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136492692</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>646499</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6943041</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492692</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1322965</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>647065</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6943550</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322965</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1323582</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lomtjärn S, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>646475</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6942960</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1323582</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1568573</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lomtjärnen S - Malarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>646461</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6942878</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2012-11-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2012-11-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog, nyckelbiotopsklass</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1568573</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1763371</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>647088</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6943543</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763371</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1763372</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>647055</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6943589</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/1763372</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136492693</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>646690</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6943229</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492693</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136492695</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>646997</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6943476</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492695</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136492694</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92493</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>646699</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6943225</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492694</t>
         </is>
       </c>
     </row>
@@ -2759,6 +3949,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136492693</v>
       </c>
       <c r="B26" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>136492694</v>
       </c>
       <c r="B28" t="n">
-        <v>92493</v>
+        <v>92494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
